--- a/spreadsheet/macrofree/azurefirewall_sg_checklist.ko.xlsx
+++ b/spreadsheet/macrofree/azurefirewall_sg_checklist.ko.xlsx
@@ -1263,7 +1263,11 @@
           <t>스포크-스포크, 스포크-인터넷 및 스포크-하이브리드 연결을 위한 기존 허브 및 스포크 아키텍처에서 Azure Firewall을 통해 트래픽을 강제 적용하도록 UDR을 구성합니다. &lt;BR&gt;&lt;BR&gt; Virtual WAN에서 허브에 통합된 Azure Firewall 인스턴스를 통해 프라이빗 트래픽 또는 인터넷 트래픽을 리디렉션하도록 라우팅 의도 및 정책을 구성합니다. &lt;BR&gt;&lt;BR&gt; UDR을 적용할 수 없고 웹 트래픽 리디렉션만 필요한 경우 아웃바운드 경로에서 Azure Firewall을 명시적 프록시로 사용합니다. Azure Firewall을 프록시로 구성할 때 웹 브라우저와 같은 전송 애플리케이션에서 프록시 설정을 구성할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>방화벽을 통해 트래픽을 전송하여 트래픽을 검사하고 악성 트래픽을 식별 및 차단할 수 있습니다. &lt;BR&gt;&lt;BR&gt; 웹 트래픽이 방화벽의 개인 IP 주소에 도달하여 UDR을 사용하지 않고 방화벽에서 직접 나가도록 Azure Firewall을 아웃바운드 트래픽에 대한 명시적 프록시로 사용합니다. 또한 이 기능을 사용하면 기존 네트워크 경로를 수정하지 않고도 여러 방화벽을 쉽게 사용할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="E14" s="21" t="n"/>
       <c r="F14" t="inlineStr">
         <is>
@@ -1361,7 +1365,11 @@
           <t>응용 프로그램 규칙에서 FQDN 태그를 사용하여 특정 Microsoft 서비스에 대한 선택적 액세스를 제공합니다. &lt;BR&gt;&lt;BR&gt; 애플리케이션 규칙에서 FQDN 태그를 사용하여 Microsoft 365, Windows 365 및 Microsoft Intune 같은 특정 Azure 서비스에 대해 방화벽을 통해 필요한 아웃바운드 네트워크 트래픽을 허용할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D17" s="21" t="n"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Azure Firewall 애플리케이션 규칙에서 FQDN 태그를 사용하여 잘 알려진 Microsoft 서비스와 연결된 FQDN 그룹을 나타냅니다. 이 방법을 사용하면 네트워크 보안 규칙의 관리가 간소화됩니다.</t>
+        </is>
+      </c>
       <c r="E17" s="21" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
@@ -1629,7 +1637,11 @@
           <t>Firewall Manager 정책, 연결 및 상속을 신중하게 검토하여 비용을 최적화합니다. 정책은 방화벽 연결을 기준으로 요금이 청구됩니다. 방화벽 연결이 0개 또는 1개인 정책은 무료입니다. 여러 방화벽 연결이 있는 정책은 고정 요율로 청구됩니다. 자세한 내용은 Firewall Manager 요금을 참조하세요.</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n"/>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Firewall Manager 및 해당 정책을 적절하게 사용하여 운영 비용을 절감하고 효율성을 높이며 관리 오버헤드를 줄입니다.</t>
+        </is>
+      </c>
       <c r="E25" s="21" t="n"/>
       <c r="F25" t="inlineStr">
         <is>
